--- a/StructureDefinition-Prov-Resurs.xlsx
+++ b/StructureDefinition-Prov-Resurs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Prov-Resurs.xlsx
+++ b/StructureDefinition-Prov-Resurs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="106">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Prov : Resurs).</t>
+    <t>Klassen Prov håller information om ett prov.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -263,6 +263,9 @@
     <t>Source attribute: id; renamed from reserved FSH name 'id'</t>
   </si>
   <si>
+    <t>Angivelse av identitetsbeteckning för ett prov.</t>
+  </si>
+  <si>
     <t>Prov-Resurs.material</t>
   </si>
   <si>
@@ -273,6 +276,11 @@
     <t>Source attribute: material</t>
   </si>
   <si>
+    <t>Kod för typ av provmaterial.
+Koden för provmaterial kan även innefatta information om provtagningsmetod.
+Om kod inte kan anges från nationellt urval kan originalText användas för textalternativ.</t>
+  </si>
+  <si>
     <t>Prov-Resurs.provtagningstidpunkt</t>
   </si>
   <si>
@@ -283,10 +291,18 @@
     <t>Source attribute: provtagningstidpunkt</t>
   </si>
   <si>
+    <t>Angivelse av den tidpunkt då ett prov är taget.</t>
+  </si>
+  <si>
     <t>Prov-Resurs.anatomiskLokalisation</t>
   </si>
   <si>
     <t>Source attribute: anatomisk lokalisation</t>
+  </si>
+  <si>
+    <t>Kod som anger var provet är taget.
+Exempel: höger arm, vänster njure.
+Om kod inte kan anges från nationellt urval kan originalText användas för textalternativ.</t>
   </si>
   <si>
     <t>Prov-Resurs.kommentar</t>
@@ -297,6 +313,9 @@
   </si>
   <si>
     <t>Source attribute: kommentar</t>
+  </si>
+  <si>
+    <t>Angivelse av kommentar om enskilt prov.</t>
   </si>
   <si>
     <t>Prov-Resurs.forvarasI</t>
@@ -909,7 +928,7 @@
         <v>81</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -977,10 +996,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1003,13 +1022,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1060,7 +1079,7 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
@@ -1077,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1103,13 +1122,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1160,7 +1179,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
@@ -1177,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1203,13 +1222,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1260,7 +1279,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1277,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1303,13 +1322,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1360,7 +1379,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1377,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1403,13 +1422,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1460,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1477,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1503,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1560,7 +1579,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1577,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1603,13 +1622,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1660,7 +1679,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
